--- a/public/exports/60183112.xlsx
+++ b/public/exports/60183112.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M86"/>
+  <dimension ref="A1:O86"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Blovstrød Teglværksvej 4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">9049272</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>490</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hillerødvej 48A</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7781533</t>
+          <t xml:space="preserve">Byparken 15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H3">
-        <v>4634</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2364764</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J3">
+        <v>425</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollerødvej 8A</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248518</t>
+          <t xml:space="preserve">Byparken 27</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2364764</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H4">
-        <v>628</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4">
+        <v>425</v>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollerødvej 8B</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248518</t>
+          <t xml:space="preserve">Hillerødvej 48A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>443</v>
+          <t xml:space="preserve">3540</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7781533</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J5">
+        <v>4634</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 1B</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249027</t>
+          <t xml:space="preserve">Kollerødvej 8A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H6">
-        <v>555</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2248518</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J6">
+        <v>628</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2253190</t>
+          <t xml:space="preserve">Kollerødvej 8B</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H7">
-        <v>3715</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2248518</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J7">
+        <v>443</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2253190</t>
+          <t xml:space="preserve">Kongevejen 80A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H8">
-        <v>1773</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366025</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J8">
+        <v>405</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2253190</t>
+          <t xml:space="preserve">Poppelvej 1B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H9">
-        <v>950</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249027</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J9">
+        <v>555</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,53 +701,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2253190</t>
+          <t xml:space="preserve">Skovmosen 8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H10">
-        <v>1075</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9049227</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>450</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,53 +776,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">2253190</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H11">
-        <v>1502</v>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J11">
+        <v>3715</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,53 +851,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 1</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364764</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H12">
-        <v>425</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2253190</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022309</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
-        </is>
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>1773</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-10-14</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 15</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364764</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H13">
-        <v>425</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2253190</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022314</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J13">
+        <v>950</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2019-10-14</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Byparken 27</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2364764</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H14">
-        <v>425</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2253190</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">200022314</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>1075</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2019-10-14</t>
-        </is>
-      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevang 21</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">7636835</t>
+          <t xml:space="preserve">Søparken 1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H15">
-        <v>320</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2253190</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030530</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
-        </is>
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>1502</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-20</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elmedalen 2A</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252021</t>
+          <t xml:space="preserve">Byparken 1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2364764</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H16">
-        <v>467</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200031056</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
-        </is>
+      <c r="J16">
+        <v>425</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-04</t>
+          <t xml:space="preserve">200022309</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Henrik Larsen Rådgivende Ingeniørfirma A/S</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019-10-14</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langkæret 66</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8165981</t>
+          <t xml:space="preserve">Ørnevang 21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7636835</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H17">
-        <v>560</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200032047</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17">
+        <v>320</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200030530</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-06-01</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-04-20</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestvej 39</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2249156</t>
+          <t xml:space="preserve">Elmedalen 2A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t xml:space="preserve">3540</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2252021</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H18">
-        <v>280</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200036754</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18">
+        <v>467</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200031056</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2020-09-09</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-05-04</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,53 +1376,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkehaven 2</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2248590</t>
+          <t xml:space="preserve">Langkæret 66</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
+          <t xml:space="preserve">3540</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8165981</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H19">
-        <v>1412</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">310027452</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
-        </is>
+      <c r="J19">
+        <v>560</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-02-28</t>
+          <t xml:space="preserve">200032047</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-06-01</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1261,53 +1451,63 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovmosen 8</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049227</t>
+          <t xml:space="preserve">Vestvej 39</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H20">
-        <v>450</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2249156</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311053017</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Find Madsen Consult Aps</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J20">
+        <v>280</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-05-08</t>
+          <t xml:space="preserve">200036754</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t xml:space="preserve">COWI A/S (Kongens Lyngby)</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2020-09-09</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1326,55 +1526,65 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedalen 2</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">3540</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124821</t>
+          <t xml:space="preserve">Kirkehaven 2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2248590</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H21">
-        <v>2170</v>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311442016</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
-        </is>
+      <c r="J21">
+        <v>1412</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-08</t>
+          <t xml:space="preserve">310027452</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">JDM Rådgivende Ingeniør ApS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2023-02-28</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedalen 6</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kokkedalen 2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8124820</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8124821</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H22">
-        <v>1518</v>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311442019</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22">
+        <v>2170</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311442016</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedalen 7</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kokkedalen 6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2252633</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8124820</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H23">
-        <v>442</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311442014</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23">
+        <v>1518</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311442019</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongevejen 80A</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366025</t>
+          <t xml:space="preserve">Kokkedalen 7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
+          <t xml:space="preserve">3540</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2252633</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H24">
-        <v>405</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311442049</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24">
+        <v>442</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311442014</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lyngevej 198</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">9049169</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H25">
+      <c r="J25">
         <v>1698</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t xml:space="preserve">311442036</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lærkenborg Alle 1A</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H26">
+      <c r="J26">
         <v>1305</v>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t xml:space="preserve">311442033</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lærkenborg Alle 1B</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H27">
+      <c r="J27">
         <v>1889</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t xml:space="preserve">311442032</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rådhusvej 5</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H28">
+      <c r="J28">
         <v>7622</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t xml:space="preserve">311442020</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rådhusvej 5</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H29">
+      <c r="J29">
         <v>456</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t xml:space="preserve">311442031</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rådhusvej 5</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H30">
+      <c r="J30">
         <v>267</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t xml:space="preserve">311442020</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vestvej 20</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">2251217</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t xml:space="preserve">14</t>
         </is>
       </c>
-      <c r="H31">
+      <c r="J31">
         <v>423</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">311442029</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t xml:space="preserve">Græsmarken 2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">9049278</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H32">
+      <c r="J32">
         <v>370</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t xml:space="preserve">311447329</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Græsmarken 4</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">9049278</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H33">
+      <c r="J33">
         <v>715</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t xml:space="preserve">311447332</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Uglevang 3</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">2248336</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H34">
+      <c r="J34">
         <v>616</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t xml:space="preserve">311447323</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t xml:space="preserve">Uglevang 7</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">2248336</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H35">
+      <c r="J35">
         <v>796</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t xml:space="preserve">311447326</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-01</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t xml:space="preserve">Violvej 1</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">8353630</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H36">
+      <c r="J36">
         <v>620</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t xml:space="preserve">311447726</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-03</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t xml:space="preserve">Violvej 3</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">8353630</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H37">
+      <c r="J37">
         <v>399</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t xml:space="preserve">311447726</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-03</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t xml:space="preserve">Violvej 5</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">8353630</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H38">
+      <c r="J38">
         <v>399</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t xml:space="preserve">311447726</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-03</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
           <t xml:space="preserve">Violvej 7</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">8353630</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H39">
+      <c r="J39">
         <v>334</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t xml:space="preserve">311447726</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-07-03</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t xml:space="preserve">Blommevej 1</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">8051620</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H40">
+      <c r="J40">
         <v>560</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t xml:space="preserve">311465973</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t xml:space="preserve">Blommevej 2</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve">8051619</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H41">
+      <c r="J41">
         <v>560</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t xml:space="preserve">311465975</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søparken 3</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">2253189</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H42">
+      <c r="J42">
         <v>580</v>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t xml:space="preserve">311465969</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Søparken 5</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">2253192</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>319</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">311465970</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ørnevang 19</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">2248320</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>614</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">311465966</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-10-08</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kirsebærgården 5</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">2250982</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>345</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311481004</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="K45" t="inlineStr">
         <is>
+          <t xml:space="preserve">311481010</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
           <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Prøvestensvej 6</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>412</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">311481008</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Elmedalen 2C</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">2251908</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>603</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">311483262</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hillerødvej 2</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">9049247</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>365</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">311483264</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vassingerød Bygade 2A</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">2260902</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>1737</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">311483277</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-12-16</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3211,53 +3701,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kirkehaven 10</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">2248517</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>364</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">311487064</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-01-12</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3276,53 +3776,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kirkehaven 16</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">2248517</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H51">
+      <c r="J51">
         <v>766</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">311487061</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-01-12</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3341,53 +3851,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lyngevej 202</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">8262928</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>628</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">311492240</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-02</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3406,53 +3926,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Sortemosevej 20</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">2364583</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>2250</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">311492237</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-02</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3471,53 +4001,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Møllemosevej 5</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">8975861</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>1956</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">311495495</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-15</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3536,53 +4076,63 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 17</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">2248417</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>280</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">311498020</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-02-24</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3601,53 +4151,63 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skovensvej 10</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">717763</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">33</t>
         </is>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>441</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">311501694</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-09</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3666,53 +4226,63 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skovensvej 4</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">8283542</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H57">
+      <c r="J57">
         <v>2779</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">311503486</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,53 +4301,63 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Skovensvej 8</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">8283542</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H58">
+      <c r="J58">
         <v>1122</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">311503486</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-03-15</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3796,53 +4376,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rørmosevænget 2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">9366855</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>473</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">311524794</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-06-02</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3861,53 +4451,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Gadekæret 15</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t xml:space="preserve">8124816</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>1640</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">311567091</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3926,53 +4526,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Gadekæret 15</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t xml:space="preserve">8124816</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>5453</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">311567091</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3991,53 +4601,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kokkedalen 11</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">8124816</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">21</t>
         </is>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>401</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">311569165</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4056,53 +4676,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Gadekæret 15</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">8124816</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>695</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">311569139</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4121,53 +4751,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ved Gadekæret 15</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">8124816</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H64">
+      <c r="J64">
         <v>1028</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">311569140</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-21</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4186,53 +4826,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Idrætsvej 14</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">9023368</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>4098</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">311569490</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4251,53 +4901,63 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Vassingerødvej 2</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">3540</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">2260918</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>608</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">311569491</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">2031-12-22</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4316,53 +4976,63 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Banevang 7</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">9049125</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>5385</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">311570453</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,53 +5051,63 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Bjarkesvej 2</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t xml:space="preserve">8164161</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>6273</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">311570450</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4446,53 +5126,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Poppelvej 1A</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
         <is>
           <t xml:space="preserve">8047783</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>9319</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">311570455</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4511,53 +5201,63 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Poppelvej 1A</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">8047783</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>356</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">311570455</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">2032-01-04</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4576,53 +5276,63 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådhusparken 58</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">257993, 257994</t>
+          <t xml:space="preserve">Søparken 1B</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H71">
-        <v>4748</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9049188</t>
+        </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">311635851</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sustainsolutions</t>
-        </is>
+          <t xml:space="preserve">17</t>
+        </is>
+      </c>
+      <c r="J71">
+        <v>1758</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-14</t>
+          <t xml:space="preserve">311570454</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-01-04</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4641,53 +5351,63 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 1E</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">9782444</t>
+          <t xml:space="preserve">Rådhusparken 58</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257993, 257994</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H72">
-        <v>1990</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311636414</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
-        </is>
+      <c r="J72">
+        <v>4748</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-18</t>
+          <t xml:space="preserve">311635851</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
+          <t xml:space="preserve">Sustainsolutions</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2032-10-14</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4706,53 +5426,63 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søparken 1B</t>
+          <t xml:space="preserve">Allerød Kommune</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3450</t>
+          <t xml:space="preserve">201</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">9049188</t>
+          <t xml:space="preserve">Poppelvej 1E</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
-        </is>
-      </c>
-      <c r="H73">
-        <v>1758</v>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9782444</t>
+        </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311636419</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J73">
+        <v>1990</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
+          <t xml:space="preserve">311636414</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
           <t xml:space="preserve">2032-10-18</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4771,53 +5501,63 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 61</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H74">
+      <c r="J74">
         <v>2140</v>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t xml:space="preserve">311673997</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4836,53 +5576,63 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 65</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H75">
+      <c r="J75">
         <v>3349</v>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t xml:space="preserve">311674000</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4901,53 +5651,63 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 65</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H76">
+      <c r="J76">
         <v>3264</v>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t xml:space="preserve">311674000</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4966,53 +5726,63 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 65</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H77">
+      <c r="J77">
         <v>374</v>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t xml:space="preserve">311674000</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5031,53 +5801,63 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t xml:space="preserve">Frederiksborgvej 65</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t xml:space="preserve">2249071</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H78">
+      <c r="J78">
         <v>1453</v>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t xml:space="preserve">311674000</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t xml:space="preserve">2033-04-17</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5096,53 +5876,63 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t xml:space="preserve">Fritz Hansens Vej 23</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t xml:space="preserve">2248459</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H79">
+      <c r="J79">
         <v>1566</v>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t xml:space="preserve">311784987</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t xml:space="preserve">OS Engineering ApS</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t xml:space="preserve">2034-09-16</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5161,53 +5951,63 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
           <t xml:space="preserve">Byagervej 12</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="H80">
+      <c r="J80">
         <v>1383</v>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5226,53 +6026,63 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
           <t xml:space="preserve">Byagervej 2</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H81">
+      <c r="J81">
         <v>1744</v>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5291,53 +6101,63 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
           <t xml:space="preserve">Byagervej 4</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H82">
+      <c r="J82">
         <v>1820</v>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5356,53 +6176,63 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kærvej 10</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
         </is>
       </c>
-      <c r="H83">
+      <c r="J83">
         <v>1944</v>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5421,53 +6251,63 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kærvej 10</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t xml:space="preserve">17</t>
         </is>
       </c>
-      <c r="H84">
+      <c r="J84">
         <v>2074</v>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5486,53 +6326,63 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kærvej 10</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t xml:space="preserve">18</t>
         </is>
       </c>
-      <c r="H85">
+      <c r="J85">
         <v>962</v>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -5551,59 +6401,69 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t xml:space="preserve">201</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
+          <t xml:space="preserve">Allerød Kommune</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kærvej 6</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3450</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3450</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t xml:space="preserve">2364446</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H86">
+      <c r="J86">
         <v>2313</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t xml:space="preserve">311898269</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-05-01</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M86"/>
+  <autoFilter ref="A1:O86"/>
 </worksheet>
 </file>
--- a/public/exports/60183112.xlsx
+++ b/public/exports/60183112.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442036</t>
+          <t xml:space="preserve">311442038</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">

--- a/public/exports/60183112.xlsx
+++ b/public/exports/60183112.xlsx
@@ -1864,7 +1864,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442038</t>
+          <t xml:space="preserve">311442036</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
